--- a/public/geografia-cr-completa.xlsx
+++ b/public/geografia-cr-completa.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="435">
   <si>
     <t>Provincia</t>
   </si>
@@ -949,6 +949,9 @@
     <t>Río Naranjo</t>
   </si>
   <si>
+    <t>Pijije</t>
+  </si>
+  <si>
     <t>Carrillo</t>
   </si>
   <si>
@@ -1123,6 +1126,9 @@
     <t>Brunka</t>
   </si>
   <si>
+    <t>Cabagra</t>
+  </si>
+  <si>
     <t>Montes de Oro</t>
   </si>
   <si>
@@ -1307,6 +1313,9 @@
   </si>
   <si>
     <t>Río Jiménez</t>
+  </si>
+  <si>
+    <t>Duacarí</t>
   </si>
 </sst>
 </file>
@@ -1687,7 +1696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C492"/>
+  <dimension ref="A1:C495"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -5726,10 +5735,10 @@
         <v>289</v>
       </c>
       <c r="B367" t="s">
+        <v>309</v>
+      </c>
+      <c r="C367" t="s">
         <v>312</v>
-      </c>
-      <c r="C367" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
@@ -5737,10 +5746,10 @@
         <v>289</v>
       </c>
       <c r="B368" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C368" t="s">
-        <v>190</v>
+        <v>314</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
@@ -5748,10 +5757,10 @@
         <v>289</v>
       </c>
       <c r="B369" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C369" t="s">
-        <v>314</v>
+        <v>190</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
@@ -5759,10 +5768,10 @@
         <v>289</v>
       </c>
       <c r="B370" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C370" t="s">
-        <v>276</v>
+        <v>315</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
@@ -5770,10 +5779,10 @@
         <v>289</v>
       </c>
       <c r="B371" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C371" t="s">
-        <v>315</v>
+        <v>276</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
@@ -5781,10 +5790,10 @@
         <v>289</v>
       </c>
       <c r="B372" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C372" t="s">
-        <v>190</v>
+        <v>316</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
@@ -5792,10 +5801,10 @@
         <v>289</v>
       </c>
       <c r="B373" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C373" t="s">
-        <v>19</v>
+        <v>190</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
@@ -5803,10 +5812,10 @@
         <v>289</v>
       </c>
       <c r="B374" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C374" t="s">
-        <v>316</v>
+        <v>19</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -5814,7 +5823,7 @@
         <v>289</v>
       </c>
       <c r="B375" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C375" t="s">
         <v>317</v>
@@ -5825,10 +5834,10 @@
         <v>289</v>
       </c>
       <c r="B376" t="s">
+        <v>316</v>
+      </c>
+      <c r="C376" t="s">
         <v>318</v>
-      </c>
-      <c r="C376" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
@@ -5836,7 +5845,7 @@
         <v>289</v>
       </c>
       <c r="B377" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C377" t="s">
         <v>320</v>
@@ -5847,10 +5856,10 @@
         <v>289</v>
       </c>
       <c r="B378" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C378" t="s">
-        <v>86</v>
+        <v>321</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
@@ -5858,10 +5867,10 @@
         <v>289</v>
       </c>
       <c r="B379" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C379" t="s">
-        <v>321</v>
+        <v>86</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -5869,7 +5878,7 @@
         <v>289</v>
       </c>
       <c r="B380" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C380" t="s">
         <v>322</v>
@@ -5880,7 +5889,7 @@
         <v>289</v>
       </c>
       <c r="B381" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C381" t="s">
         <v>323</v>
@@ -5891,7 +5900,7 @@
         <v>289</v>
       </c>
       <c r="B382" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C382" t="s">
         <v>324</v>
@@ -5902,10 +5911,10 @@
         <v>289</v>
       </c>
       <c r="B383" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C383" t="s">
-        <v>246</v>
+        <v>325</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
@@ -5913,10 +5922,10 @@
         <v>289</v>
       </c>
       <c r="B384" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C384" t="s">
-        <v>325</v>
+        <v>246</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
@@ -5924,7 +5933,7 @@
         <v>289</v>
       </c>
       <c r="B385" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C385" t="s">
         <v>326</v>
@@ -5935,7 +5944,7 @@
         <v>289</v>
       </c>
       <c r="B386" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C386" t="s">
         <v>327</v>
@@ -5946,7 +5955,7 @@
         <v>289</v>
       </c>
       <c r="B387" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C387" t="s">
         <v>328</v>
@@ -5957,10 +5966,10 @@
         <v>289</v>
       </c>
       <c r="B388" t="s">
+        <v>323</v>
+      </c>
+      <c r="C388" t="s">
         <v>329</v>
-      </c>
-      <c r="C388" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
@@ -5968,10 +5977,10 @@
         <v>289</v>
       </c>
       <c r="B389" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C389" t="s">
-        <v>213</v>
+        <v>331</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
@@ -5979,10 +5988,10 @@
         <v>289</v>
       </c>
       <c r="B390" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C390" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -5990,10 +5999,10 @@
         <v>289</v>
       </c>
       <c r="B391" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C391" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
@@ -6001,10 +6010,10 @@
         <v>289</v>
       </c>
       <c r="B392" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C392" t="s">
-        <v>331</v>
+        <v>100</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -6012,7 +6021,7 @@
         <v>289</v>
       </c>
       <c r="B393" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C393" t="s">
         <v>332</v>
@@ -6023,7 +6032,7 @@
         <v>289</v>
       </c>
       <c r="B394" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C394" t="s">
         <v>333</v>
@@ -6034,7 +6043,7 @@
         <v>289</v>
       </c>
       <c r="B395" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C395" t="s">
         <v>334</v>
@@ -6045,7 +6054,7 @@
         <v>289</v>
       </c>
       <c r="B396" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C396" t="s">
         <v>335</v>
@@ -6056,7 +6065,7 @@
         <v>289</v>
       </c>
       <c r="B397" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C397" t="s">
         <v>336</v>
@@ -6067,7 +6076,7 @@
         <v>289</v>
       </c>
       <c r="B398" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C398" t="s">
         <v>337</v>
@@ -6078,7 +6087,7 @@
         <v>289</v>
       </c>
       <c r="B399" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C399" t="s">
         <v>338</v>
@@ -6089,7 +6098,7 @@
         <v>289</v>
       </c>
       <c r="B400" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C400" t="s">
         <v>339</v>
@@ -6100,7 +6109,7 @@
         <v>289</v>
       </c>
       <c r="B401" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C401" t="s">
         <v>340</v>
@@ -6111,7 +6120,7 @@
         <v>289</v>
       </c>
       <c r="B402" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C402" t="s">
         <v>341</v>
@@ -6119,10 +6128,10 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>342</v>
+        <v>289</v>
       </c>
       <c r="B403" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C403" t="s">
         <v>342</v>
@@ -6130,10 +6139,10 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B404" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C404" t="s">
         <v>343</v>
@@ -6141,10 +6150,10 @@
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B405" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C405" t="s">
         <v>344</v>
@@ -6152,10 +6161,10 @@
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B406" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C406" t="s">
         <v>345</v>
@@ -6163,10 +6172,10 @@
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B407" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C407" t="s">
         <v>346</v>
@@ -6174,10 +6183,10 @@
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B408" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C408" t="s">
         <v>347</v>
@@ -6185,10 +6194,10 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B409" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C409" t="s">
         <v>348</v>
@@ -6196,10 +6205,10 @@
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B410" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C410" t="s">
         <v>349</v>
@@ -6207,10 +6216,10 @@
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B411" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C411" t="s">
         <v>350</v>
@@ -6218,10 +6227,10 @@
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B412" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C412" t="s">
         <v>351</v>
@@ -6229,10 +6238,10 @@
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B413" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C413" t="s">
         <v>352</v>
@@ -6240,10 +6249,10 @@
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B414" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C414" t="s">
         <v>353</v>
@@ -6251,10 +6260,10 @@
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B415" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C415" t="s">
         <v>354</v>
@@ -6262,10 +6271,10 @@
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B416" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C416" t="s">
         <v>355</v>
@@ -6273,10 +6282,10 @@
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B417" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C417" t="s">
         <v>356</v>
@@ -6284,21 +6293,21 @@
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B418" t="s">
+        <v>343</v>
+      </c>
+      <c r="C418" t="s">
         <v>357</v>
-      </c>
-      <c r="C418" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B419" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C419" t="s">
         <v>359</v>
@@ -6306,10 +6315,10 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B420" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C420" t="s">
         <v>360</v>
@@ -6317,62 +6326,62 @@
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B421" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C421" t="s">
-        <v>17</v>
+        <v>361</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B422" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C422" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B423" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C423" t="s">
-        <v>361</v>
+        <v>93</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B424" t="s">
-        <v>163</v>
+        <v>358</v>
       </c>
       <c r="C424" t="s">
-        <v>163</v>
+        <v>362</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B425" t="s">
         <v>163</v>
       </c>
       <c r="C425" t="s">
-        <v>362</v>
+        <v>163</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B426" t="s">
         <v>163</v>
@@ -6383,7 +6392,7 @@
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B427" t="s">
         <v>163</v>
@@ -6394,7 +6403,7 @@
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B428" t="s">
         <v>163</v>
@@ -6405,7 +6414,7 @@
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B429" t="s">
         <v>163</v>
@@ -6416,7 +6425,7 @@
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B430" t="s">
         <v>163</v>
@@ -6427,7 +6436,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B431" t="s">
         <v>163</v>
@@ -6438,7 +6447,7 @@
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B432" t="s">
         <v>163</v>
@@ -6449,65 +6458,65 @@
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B433" t="s">
+        <v>163</v>
+      </c>
+      <c r="C433" t="s">
         <v>370</v>
-      </c>
-      <c r="C433" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B434" t="s">
-        <v>370</v>
+        <v>163</v>
       </c>
       <c r="C434" t="s">
-        <v>231</v>
+        <v>371</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B435" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C435" t="s">
-        <v>75</v>
+        <v>373</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B436" t="s">
         <v>372</v>
       </c>
       <c r="C436" t="s">
-        <v>373</v>
+        <v>231</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B437" t="s">
         <v>372</v>
       </c>
       <c r="C437" t="s">
-        <v>374</v>
+        <v>75</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B438" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C438" t="s">
         <v>375</v>
@@ -6515,10 +6524,10 @@
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B439" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C439" t="s">
         <v>376</v>
@@ -6526,10 +6535,10 @@
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B440" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C440" t="s">
         <v>377</v>
@@ -6537,10 +6546,10 @@
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B441" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C441" t="s">
         <v>378</v>
@@ -6548,10 +6557,10 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B442" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C442" t="s">
         <v>379</v>
@@ -6559,10 +6568,10 @@
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B443" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C443" t="s">
         <v>380</v>
@@ -6570,10 +6579,10 @@
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B444" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C444" t="s">
         <v>381</v>
@@ -6581,10 +6590,10 @@
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B445" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C445" t="s">
         <v>382</v>
@@ -6592,10 +6601,10 @@
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B446" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C446" t="s">
         <v>383</v>
@@ -6603,10 +6612,10 @@
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B447" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C447" t="s">
         <v>384</v>
@@ -6614,32 +6623,32 @@
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B448" t="s">
+        <v>384</v>
+      </c>
+      <c r="C448" t="s">
         <v>385</v>
-      </c>
-      <c r="C448" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B449" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C449" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B450" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C450" t="s">
         <v>388</v>
@@ -6647,10 +6656,10 @@
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B451" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C451" t="s">
         <v>389</v>
@@ -6658,10 +6667,10 @@
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B452" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C452" t="s">
         <v>390</v>
@@ -6669,10 +6678,10 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B453" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C453" t="s">
         <v>391</v>
@@ -6680,10 +6689,10 @@
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B454" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C454" t="s">
         <v>392</v>
@@ -6691,32 +6700,32 @@
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B455" t="s">
+        <v>387</v>
+      </c>
+      <c r="C455" t="s">
         <v>393</v>
-      </c>
-      <c r="C455" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B456" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C456" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B457" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C457" t="s">
         <v>396</v>
@@ -6724,10 +6733,10 @@
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B458" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C458" t="s">
         <v>397</v>
@@ -6735,32 +6744,32 @@
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B459" t="s">
+        <v>395</v>
+      </c>
+      <c r="C459" t="s">
         <v>398</v>
-      </c>
-      <c r="C459" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B460" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C460" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B461" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C461" t="s">
         <v>401</v>
@@ -6768,10 +6777,10 @@
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B462" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C462" t="s">
         <v>402</v>
@@ -6779,10 +6788,10 @@
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B463" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C463" t="s">
         <v>403</v>
@@ -6790,7 +6799,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>404</v>
+        <v>343</v>
       </c>
       <c r="B464" t="s">
         <v>404</v>
@@ -6801,10 +6810,10 @@
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>404</v>
+        <v>343</v>
       </c>
       <c r="B465" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C465" t="s">
         <v>405</v>
@@ -6812,10 +6821,10 @@
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B466" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C466" t="s">
         <v>406</v>
@@ -6823,10 +6832,10 @@
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B467" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C467" t="s">
         <v>407</v>
@@ -6834,54 +6843,54 @@
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B468" t="s">
+        <v>406</v>
+      </c>
+      <c r="C468" t="s">
         <v>408</v>
-      </c>
-      <c r="C468" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B469" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C469" t="s">
-        <v>235</v>
+        <v>409</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B470" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C470" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B471" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C471" t="s">
-        <v>411</v>
+        <v>235</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B472" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C472" t="s">
         <v>412</v>
@@ -6889,43 +6898,43 @@
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B473" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C473" t="s">
-        <v>321</v>
+        <v>413</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B474" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C474" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B475" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C475" t="s">
-        <v>414</v>
+        <v>322</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B476" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C476" t="s">
         <v>415</v>
@@ -6933,10 +6942,10 @@
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B477" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C477" t="s">
         <v>416</v>
@@ -6944,10 +6953,10 @@
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B478" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C478" t="s">
         <v>417</v>
@@ -6955,10 +6964,10 @@
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B479" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C479" t="s">
         <v>418</v>
@@ -6966,10 +6975,10 @@
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B480" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C480" t="s">
         <v>419</v>
@@ -6977,10 +6986,10 @@
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B481" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C481" t="s">
         <v>420</v>
@@ -6988,32 +6997,32 @@
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B482" t="s">
+        <v>416</v>
+      </c>
+      <c r="C482" t="s">
         <v>421</v>
-      </c>
-      <c r="C482" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B483" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C483" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B484" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C484" t="s">
         <v>424</v>
@@ -7021,10 +7030,10 @@
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B485" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C485" t="s">
         <v>425</v>
@@ -7032,10 +7041,10 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B486" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C486" t="s">
         <v>426</v>
@@ -7043,10 +7052,10 @@
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B487" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C487" t="s">
         <v>427</v>
@@ -7054,10 +7063,10 @@
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B488" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C488" t="s">
         <v>428</v>
@@ -7065,10 +7074,10 @@
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B489" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C489" t="s">
         <v>429</v>
@@ -7076,39 +7085,72 @@
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B490" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C490" t="s">
-        <v>98</v>
+        <v>430</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B491" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C491" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B492" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C492" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>406</v>
+      </c>
+      <c r="B493" t="s">
         <v>431</v>
+      </c>
+      <c r="C493" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>406</v>
+      </c>
+      <c r="B494" t="s">
+        <v>431</v>
+      </c>
+      <c r="C494" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>406</v>
+      </c>
+      <c r="B495" t="s">
+        <v>431</v>
+      </c>
+      <c r="C495" t="s">
+        <v>434</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>